--- a/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
@@ -1272,13 +1272,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51A83BFB-F4F6-4FD9-B470-69B1B58FD0E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75531E13-1CEF-48DE-9750-ACD3BFE63CC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B58B2D-9838-43F0-9B43-E7D9A934BF73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA5BB70-632C-41BD-AB27-710EFC0313B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEE0A1F-E3E6-4956-A193-284DC94307C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C06DAB2-0BD7-4A6B-97C0-A1605439D120}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
@@ -1272,13 +1272,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75531E13-1CEF-48DE-9750-ACD3BFE63CC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91CFB3E-EF60-40A6-8A8C-5BE415DD2E71}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA5BB70-632C-41BD-AB27-710EFC0313B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CEB0679-D280-4DAF-A3E4-FCA74F627417}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C06DAB2-0BD7-4A6B-97C0-A1605439D120}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEAC168A-9B3A-4A97-A2A2-8D2C8B498D3D}"/>
 </file>
--- a/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/Supplier_Fields_Detail.xlsx
@@ -1272,13 +1272,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91CFB3E-EF60-40A6-8A8C-5BE415DD2E71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51A83BFB-F4F6-4FD9-B470-69B1B58FD0E7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CEB0679-D280-4DAF-A3E4-FCA74F627417}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B58B2D-9838-43F0-9B43-E7D9A934BF73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEAC168A-9B3A-4A97-A2A2-8D2C8B498D3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEE0A1F-E3E6-4956-A193-284DC94307C7}"/>
 </file>